--- a/2022 data/excel_outputs/16_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/16_boothwise_data.xlsx
@@ -14,1041 +14,1110 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="390">
   <si>
     <t>AC 16 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>######## ######## #0nn 1 #0##0.1 #######</t>
-  </si>
-  <si>
-    <t>######## ######## #0nn 1 #0##0.2 #######</t>
-  </si>
-  <si>
-    <t>######## ######## #0nn 1 #0##0.3 #######</t>
-  </si>
-  <si>
-    <t>######## ######## #######</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.1 #####</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.4 #####</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.2 #####</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.5 #####</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.3 #####</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### #0##0.6 #####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ########ddh #0##0.1 #######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ########ddh #0##0.2 #######</t>
-  </si>
-  <si>
-    <t>##### ###### ## #####</t>
-  </si>
-  <si>
-    <t>######## ######## #####</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.1 ####### #### #####</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.2 ####### #### #####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8########ddh #0##0.1 ######## #### #####</t>
-  </si>
-  <si>
-    <t>######## ######## ##01 ##### #0##0.1</t>
-  </si>
-  <si>
-    <t>######## ######## ##01 ##### #0##0.#</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;6 ## 8ddh #0##0.1 #####</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.1 ####### #### #######</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.2 ####### #### #######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ########ddh #0##0.1 ##### ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ########ddh #### ##0.3 ##### ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ########ddh #### ##0.2 ##### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ######## #####</t>
-  </si>
-  <si>
-    <t>######## ######## ##0#0.1 ########</t>
-  </si>
-  <si>
-    <t>######## ######## ##0#0nn2 ########</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ########ddh #0##0.1 ########</t>
-  </si>
-  <si>
-    <t>##### ####### ########</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.1 #0##0.1 #####</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.1 #0##0.2 #####</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.2 #0##0.1 #####</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.2 #0##0.2 #####</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.1 #######</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.2 #######</t>
-  </si>
-  <si>
-    <t>##### #### ######## ######## ;6 ## 8ddh ######</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.1 ##########</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.2 ##########</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.3 ##########</t>
-  </si>
-  <si>
-    <t>######## ######## ### ### #0##0.1 #####</t>
-  </si>
-  <si>
-    <t>######## ######## ### ### #0##0.3 #####</t>
-  </si>
-  <si>
-    <t>######## ######## ### ### #0##0.2 #####</t>
-  </si>
-  <si>
-    <t>######## ######## ### ### #0##0.4 #####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;6 ## 8ddh #0##0.2 #####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;6 ## 8ddh #0##0.3 #####</t>
-  </si>
-  <si>
-    <t>###### ## #####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ########ddh #0##0.1 ############ #### #####</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.1 ######## #####</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.2 ######## #####</t>
-  </si>
-  <si>
-    <t>######## ######## ######## #### ######## #####</t>
-  </si>
-  <si>
-    <t>######## ######## #0#0.1 ######### #### ######## #####</t>
-  </si>
-  <si>
-    <t>######## ######## #0#0.2 ######### #### ######## #####</t>
-  </si>
-  <si>
-    <t>#### ##### #### ##0.1 ########</t>
-  </si>
-  <si>
-    <t>#### ##### #### ##0.8 ########</t>
-  </si>
-  <si>
-    <t>#### ##### #### ##0.2 ########</t>
-  </si>
-  <si>
-    <t>#### ##### #### ##0.7 ########</t>
-  </si>
-  <si>
-    <t>#### ##### #### ##0.3 ########</t>
-  </si>
-  <si>
-    <t>#### ##### #### ##0.4 ########</t>
-  </si>
-  <si>
-    <t>#### ##### #### ##0.6 ########</t>
-  </si>
-  <si>
-    <t>#### ##### #### ##0.5 ########</t>
-  </si>
-  <si>
-    <t>#### ##### #### ##0.9 ########</t>
-  </si>
-  <si>
-    <t>######## ######## ##0 5 #0##0.1 ########</t>
-  </si>
-  <si>
-    <t>######## ######## ##0 5 #0##0.2 ########</t>
-  </si>
-  <si>
-    <t>######## ### ###### ########</t>
-  </si>
-  <si>
-    <t>######## ######## ##0 1 #0##0.1 ########</t>
-  </si>
-  <si>
-    <t>######## ######## ##0 1 #0##0.2 ########</t>
-  </si>
-  <si>
-    <t>######## ######## ##0 1 #0##0.3 ########</t>
-  </si>
-  <si>
-    <t>######## ######## #0#0.1 ####### #### #########</t>
-  </si>
-  <si>
-    <t>######## ######## #0#0.1 #########</t>
-  </si>
-  <si>
-    <t>######## ######## #0#0.1 ######### #####</t>
-  </si>
-  <si>
-    <t>######## ######## #0#0.2 ######### #####</t>
-  </si>
-  <si>
-    <t>###### ## ######## ####</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0 2 ######## #####</t>
-  </si>
-  <si>
-    <t>######## ##### ####### #### ########</t>
-  </si>
-  <si>
-    <t>######## ######## ########</t>
-  </si>
-  <si>
-    <t>######## ######## #0#0.1 ######</t>
-  </si>
-  <si>
-    <t>######## ##### ######## #0##0.1 ########</t>
-  </si>
-  <si>
-    <t>######## ##### ######## #0##0.2 ########</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ######## ddh #0##0 1 ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ######## ddh #0##0 2 ####</t>
-  </si>
-  <si>
-    <t>######## ######## #### ##0.1 ########</t>
-  </si>
-  <si>
-    <t>######## ######## #### ##0.2 ########</t>
-  </si>
-  <si>
-    <t>######## ######## #### ##0.3 ########</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0.1 ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0.2 ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0.3 ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0.4 ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0.5 ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0.6 ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0.7 ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0.8 ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0.9 ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0.10 ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0 1 #### #######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0 2 #### #######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0 3 #### #######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0 4 #### #######</t>
-  </si>
-  <si>
-    <t>######## ######## ######### #### ###########</t>
-  </si>
-  <si>
-    <t>######## ######## ##01 ###### ##0##0.1</t>
-  </si>
-  <si>
-    <t>######## ######## ##01 ###### ##0##0.2</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0.1 #######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0.2 #######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #### ##0.1 ######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #### ##0.2 ######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ########ddh #### ##0.3 ######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0 1 ##### ##0##0.1</t>
-  </si>
-  <si>
-    <t>######## ######## ##0 1 ##### ##0##0.3</t>
-  </si>
-  <si>
-    <t>######## ######## ##0 1 ##### ##0##0.2</t>
-  </si>
-  <si>
-    <t>##0##0 #### ##### #### ##03 #####</t>
-  </si>
-  <si>
-    <t>##0##0 #### ##### #### ##08 #####</t>
-  </si>
-  <si>
-    <t>##0##0 #### ##### #### ##04 #####</t>
-  </si>
-  <si>
-    <t>##0##0 #### ##### #### ##07 #####</t>
-  </si>
-  <si>
-    <t>##0##0 #### ##### #### ##05 #####</t>
-  </si>
-  <si>
-    <t>##0##0 #### ##### #### ##09 #####</t>
-  </si>
-  <si>
-    <t>##0##0 #### ##### #### ##06 #####</t>
-  </si>
-  <si>
-    <t>#### ######## ########1 ## 8 ######## #0##0.2 #######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.1 #####</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.2 #####</t>
-  </si>
-  <si>
-    <t>######## ######## ##0 2 #0##0.1 ##### #####</t>
-  </si>
-  <si>
-    <t>######## ######## ##0 2 ##0##0.4 ##### ############# ######## ##0 2 ##0##0.4 ##### #####</t>
-  </si>
-  <si>
-    <t>######## ######## ##0 2 #0##0.2 ##### #####</t>
-  </si>
-  <si>
-    <t>######## ######## ##0 2 #0##0.6 ##### #####</t>
-  </si>
-  <si>
-    <t>######## ######## ##0 2 #0##0.3 ##### #####</t>
-  </si>
-  <si>
-    <t>######## ######## ##0 2 #0##0.5 ###### #####</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.1 ########</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.2 ########</t>
-  </si>
-  <si>
-    <t>##### ##### ######## #0##0 2 ########</t>
-  </si>
-  <si>
-    <t>##### ##### ######## #0##0 4 ########</t>
-  </si>
-  <si>
-    <t>##### ##### ######## #0##0 3 ########</t>
-  </si>
-  <si>
-    <t>##### ##### ######## #0##0 5 ########</t>
-  </si>
-  <si>
-    <t>######## ######## ##### 1 #########</t>
-  </si>
-  <si>
-    <t>######## ######## ##### 2 #########</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.1 ######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.2 ######</t>
-  </si>
-  <si>
-    <t>#### ###### ### ##### ##0##0.1 ######</t>
-  </si>
-  <si>
-    <t>#### ###### ### ##### ##0##0.2 ######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;6 ## 8ddh #0##0.1 ######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;6 ## 8ddh #0##0.4 ######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;6 ## 8ddh #0##0.2 ######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;6 ## 8ddh #0##0.3 ######</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.1 ######</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.2 ######</t>
-  </si>
-  <si>
-    <t>#### ########## ######## ;1 ## 8 ######## ddh #0##0 1 ###### #### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.1 ###### #######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.2 ###### #######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.3 ###### #######</t>
-  </si>
-  <si>
-    <t>######## ####### ##0##0.2 ###### #######</t>
-  </si>
-  <si>
-    <t>######## ####### ##0##0.1 ###### #######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ######## ddh #### #0 1 ########## #### ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ######## ddh #### #0 2 ########## #### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.1 ####</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.3 ##### ###### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.2 ####</t>
-  </si>
-  <si>
-    <t>######## ######## #### ####### ###### ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;6 ## 8ddh ##0##0.1 ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;6 ## 8ddh ##0##0.2 ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ######## ddh #### #####.1 #### #########</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ######## ddh #### #####.2 #### #########</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ######## ddh #### #####.3 #### #########</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ######## ddh #### #####.4 #### #########</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ######## ddh #0##0.1 #####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ######## ddh #0##0.2 #####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ######## ddh #0##0.3 #####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ######## ddh #0##0.4 #####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ######## ddh #0##0.5 #####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ######## ddh #0##0.6 #####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ######## ddh #0##0.7 #####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0.3 #######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0.4 #######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0.5 #######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0.6 #######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0.7 #######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;6 ## 8ddh #0##01 ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;6 ## 8ddh #0##0 2 ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0 1 ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0 2 ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0 3 ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0 4 ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0 5 ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0 6 ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0 7 ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0.1 ######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0.2 ######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0.3 ######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0.4 ######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.2 ###### #0##0.4</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### ######</t>
-  </si>
-  <si>
-    <t>######## ######## #### #0 1 #######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.2 #######</t>
-  </si>
-  <si>
-    <t>##### ##### ##### #0#0 1 ######</t>
-  </si>
-  <si>
-    <t>##### ##### ##### #0#0 2 ######</t>
-  </si>
-  <si>
-    <t>##### ##### ##### #0#0 3 ######</t>
-  </si>
-  <si>
-    <t>##### ##### ##### #0#0 4 ######</t>
-  </si>
-  <si>
-    <t>##### ##### ##### #0#0 5 ######</t>
-  </si>
-  <si>
-    <t>##### ##### ##### #0#0 6 ######</t>
-  </si>
-  <si>
-    <t>##### ##### ##### #0#0 7 ######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0 2 ##0##0.1 ######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0 2 ##0##0.2 ######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0 1 ##0##0.1 ######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0 1 ##0##0.3 ######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0 1 ##0##0.2 ######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0 1 ##0##0.4 ######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## ###### #### ##0.1</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## ###### #### ##0.2</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## ###### #### ##0.3</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## ###### #### ##0.4</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## ###### #### ##0.5</t>
-  </si>
-  <si>
-    <t>######## ######## ##0 1 ##0##0.# ########</t>
-  </si>
-  <si>
-    <t>######## ######## ##0 1 ######## #### ########</t>
-  </si>
-  <si>
-    <t>##### ###### ## ########</t>
-  </si>
-  <si>
-    <t>##### ## ### #### ########</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 6 ## 8 #0##0.1 #########</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 6 ## 8 #0##0.2 #########</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 6 ## 8 #0##0.3 #########</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 6 ## 8 #0##0.4 #########</t>
-  </si>
-  <si>
-    <t>######## ######## ### ### #0##0.1 #########</t>
-  </si>
-  <si>
-    <t>######## ######## ### ### #0##0.3 #########</t>
-  </si>
-  <si>
-    <t>######## ######## ### ### #0##0.2 #########</t>
-  </si>
-  <si>
-    <t>######## ######## ### ### #0##0.4 #########</t>
-  </si>
-  <si>
-    <t>###### ####### ##### ##### #0##0 1 ####</t>
-  </si>
-  <si>
-    <t>###### ####### ##### ##### #0##0 2 ####</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0 1 #####</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0 2 #####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## ####### #0##0.1</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## ####### #0##0.2</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## ####### #0##0.3</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## ####### #0##0.4</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.2 ####### #0##0.2</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.1 ########</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.2 ########</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.3 ########</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## ####### #### #0##0 1</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## ####### #### #0##0 2</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## ####### #### #0##0 3</t>
-  </si>
-  <si>
-    <t>pNcaayt ghr kmraa nN0-1 kailaapur jsmaur</t>
-  </si>
-  <si>
-    <t>pNcaayt ghr kmraa nN0-2 kailaapur jsmaur</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.1 ######### ;####ddh #### ####### #####</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.2 ######### ;####ddh #### ####### #####</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.1 ####### #####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;6 ## 8ddh #0##0.1 ##########</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;6 ## 8ddh #0##0.2 ##########</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;6 ## 8ddh #0##0.3 ##########</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;6 ## 8ddh #0##0.4 ##########</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.2 ###########</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.3 ######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.4 ######</t>
-  </si>
-  <si>
-    <t>##### ##### ####### ######</t>
-  </si>
-  <si>
-    <t>######## ##### ######## ##### 3 ####### ######</t>
-  </si>
-  <si>
-    <t>######## ##### ######## ##### 1 ####### ######</t>
-  </si>
-  <si>
-    <t>######## ##### ######## ##### 2 ####### ######</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.1 ####### ###</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.3 ####### ###</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.2 ####### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###1 #### ##0.1 #######</t>
-  </si>
-  <si>
-    <t>######## ######## ###1 ######## #### #######</t>
-  </si>
-  <si>
-    <t>######## ######## ###1 #### ##0 2 #######</t>
-  </si>
-  <si>
-    <t>######## ######## ###1 #### ##0 3 #######</t>
-  </si>
-  <si>
-    <t>######## ######## ###1 #### ##0 4 #######</t>
-  </si>
-  <si>
-    <t>####### ### #0##0 1 #######</t>
-  </si>
-  <si>
-    <t>####### ### #0##0 4 #######</t>
-  </si>
-  <si>
-    <t>####### ### #0##0 2 #######</t>
-  </si>
-  <si>
-    <t>####### ### #0##0 6 #######</t>
-  </si>
-  <si>
-    <t>####### ### #0##0 3 #######</t>
-  </si>
-  <si>
-    <t>####### ### #0##0 5 #######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.3 #### ##0.# #######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.3 #0##0.2 #######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.3 #0##0.3 #######</t>
-  </si>
-  <si>
-    <t>######### ##### ##### ##0 ##0 #0##0 1 #######</t>
-  </si>
-  <si>
-    <t>######### ##### ##### ##0 ##0 #0##0 2 #######</t>
-  </si>
-  <si>
-    <t>######### ##### ##### ##0 ##0 #0##0 4 #######</t>
-  </si>
-  <si>
-    <t>######### ##### ##### ##0 ##0 #0##0 3 #######</t>
-  </si>
-  <si>
-    <t>##### ######## #0##0 1 #######</t>
-  </si>
-  <si>
-    <t>##### ######## #0##0 4 #######</t>
-  </si>
-  <si>
-    <t>##### ######## #0##0 2 #######</t>
-  </si>
-  <si>
-    <t>##### ######## #0##0 3 #######</t>
-  </si>
-  <si>
-    <t>######## ######### ####### #0##0 3 #######</t>
-  </si>
-  <si>
-    <t>######## ### ###### ## ### #### ##0 1 #######</t>
-  </si>
-  <si>
-    <t>######## ### ###### ## #### ##0 3 #######</t>
-  </si>
-  <si>
-    <t>######## ### ###### ## ### #### ##0 2 #######</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.3 ######</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.4 ######</t>
-  </si>
-  <si>
-    <t>phaiejaam ucc praathmik vidyaaly k0nN0-3 kithauddaa</t>
-  </si>
-  <si>
-    <t>phaiejaam ucc praathmik vidyaaly k0nN0-5 kithauddaa</t>
-  </si>
-  <si>
-    <t>phaiejaam ucc praathmik vidyaaly k0nN0-4 kithauddaa</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.1 ########### #### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ######## #### ########### #### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.2 ########### #### ######</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.1 ##### ###########</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.2 ##### ###########</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.3 ##### ###########</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.4 ##### ###########</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ######## ddh #0##0 1 ######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.1 ######## #####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ########ddh ##0##0.2 ######</t>
-  </si>
-  <si>
-    <t>###### ## ########</t>
-  </si>
-  <si>
-    <t>juu0haa0skuul jiivnpurii urph ujiyaalii klaa</t>
-  </si>
-  <si>
-    <t>praa0 vi0 alluuvaalaa</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ######## ddh #0##0.1 ########</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ######## ddh #0##0.2 ########</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.1 ####### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.2 ### #### #### ####### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ####1 ##### #### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ####2 ##### #### ######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0 4 #######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0 5 #######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0 6 #######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.1 #### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ### #### #### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.2 #### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.3 #### ####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0 1 ######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0 2 ######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0 3 ######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0 4 ######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0 5 ######</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0.1 ### #### #### ######</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0 1 ########</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0 3 ########</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0 2 ########</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0 4 ########</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.1 ######### #### ########</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.5 ######### #### ########</t>
-  </si>
-  <si>
-    <t>######## ######## ##0##0.2 ######### #### ########</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ### ###### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ### ###### ####</t>
-  </si>
-  <si>
-    <t>##### ####### ######## ###### ####</t>
-  </si>
-  <si>
-    <t>######## ######## #0##0 3 ######</t>
-  </si>
-  <si>
-    <t>#### #### ###### #### ##### #0##0 1 ########</t>
-  </si>
-  <si>
-    <t>#### #### ###### #### ##### #0##0 2 ########</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ######## ddh ####### ######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ######## ddh #0##0.1 #### ######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ######## ddh #0##0.2 #### ######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ######## ddh #0##0.1 ######### #### #######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ######## ddh #0##0.2 ######### #### #######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1 ## 8 ######## ddh #0##0.3 ######### #### #######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0.1 ######### #### ######</t>
-  </si>
-  <si>
-    <t>#### ######## ######## 1 ## 8 ######## #0##0.2 ######### #### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0 1 #0##0 3 ##### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0 2 ##### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.3 #0##0.1 ##### #######</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.3 #0##0.2 ##### #######</t>
+    <t>DADADADADADADADA DADADADADADADADA DA0N 1 DA0DADA0.1 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0N 1 DA0DADA0.2 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0N 1 DA0DADA0.3 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.1 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.4 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.2 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.5 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.3 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADADA DADADADA DA0DADA0.6 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADADDHA DA0DADA0.1 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADADDHA DA0DADA0.2 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADADA DADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.1 DADADADADADADA DADADADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.2 DADADADADADADA DADADADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8DADADADADADADADADDHA DA0DADA0.1 DADADADADADADADA DADADADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA01 DADADADADA DA0DADA0.1</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA01 DADADADADA DA0DADA0.DA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;6 DADA 8DDHA DA0DADA0.1 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.1 DADADADADADADA DADADADA DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.2 DADADADADADADA DADADADA DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADADDHA DA0DADA0.1 DADADADADA DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADADDHA DADADADA DADA0.3 DADADADADA DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADADDHA DADADADA DADA0.2 DADADADADA DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADADADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DA0.1 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DA0N2 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADADDHA DA0DADA0.1 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADADADA DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0.1 DA0DADA0.1 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0.1 DA0DADA0.2 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0.2 DA0DADA0.1 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0.2 DA0DADA0.2 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.1 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.2 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADA DADADADADADADADA DADADADADADADADA ;6 DADA 8DDHA DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.1 DADADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.2 DADADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.3 DADADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADA DADADA DA0DADA0.1 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADA DADADA DA0DADA0.3 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADA DADADA DA0DADA0.2 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADA DADADA DA0DADA0.4 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;6 DADA 8DDHA DA0DADA0.2 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;6 DADA 8DDHA DA0DADA0.3 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADA DADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADADDHA DA0DADA0.1 DADADADADADADADADADADADA DADADADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.1 DADADADADADADADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.2 DADADADADADADADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADADADA DADADADA DADADADADADADADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DA0.1 DADADADADADADADADA DADADADA DADADADADADADADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DA0.2 DADADADADADADADADA DADADADA DADADADADADADADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADA DADADADA DADA0.1 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADA DADADADA DADA0.8 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADA DADADADA DADA0.2 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADA DADADADA DADA0.7 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADA DADADADA DADA0.3 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADA DADADADA DADA0.4 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADA DADADADA DADA0.6 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADA DADADADA DADA0.5 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADA DADADADA DADA0.9 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0 5 DA0DADA0.1 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0 5 DA0DADA0.2 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADA DADADADADADA DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0 1 DA0DADA0.1 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0 1 DA0DADA0.2 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0 1 DA0DADA0.3 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DA0.1 DADADADADADADA DADADADA DADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DA0.1 DADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DA0.1 DADADADADADADADADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DA0.2 DADADADADADADADADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADA DADA DADADADADADADADA DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0 2 DADADADADADADADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADA DADADADADADADA DADADADA DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DA0.1 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADA DADADADADADADADA DA0DADA0.1 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADA DADADADADADADADA DA0DADA0.2 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DA0DADA0 1 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DA0DADA0 2 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADA DADA0.1 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADA DADA0.2 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADA DADA0.3 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0.1 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0.2 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0.3 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0.4 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0.5 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0.6 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0.7 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0.8 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0.9 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0.10 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0 1 DADADADA DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0 2 DADADADA DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0 3 DADADADA DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0 4 DADADADA DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADADADADA DADADADA DADADADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA01 DADADADADADA DADA0DADA0.1</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA01 DADADADADADA DADA0DADA0.2</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0.1 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0.2 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DADADADA DADA0.1 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DADADADA DADA0.2 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADADDHA DADADADA DADA0.3 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0 1 DADADADADA DADA0DADA0.1</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0 1 DADADADADA DADA0DADA0.3</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0 1 DADADADADA DADA0DADA0.2</t>
+  </si>
+  <si>
+    <t>DADA0DADA0 DADADADA DADADADADA DADADADA DADA03 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADA0DADA0 DADADADA DADADADADA DADADADA DADA08 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADA0DADA0 DADADADA DADADADADA DADADADA DADA04 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADA0DADA0 DADADADA DADADADADA DADADADA DADA07 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADA0DADA0 DADADADA DADADADADA DADADADA DADA05 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADA0DADA0 DADADADA DADADADADA DADADADA DADA09 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADA0DADA0 DADADADA DADADADADA DADADADA DADA06 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA1 DADA 8 DADADADADADADADA DA0DADA0.2 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.1 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.2 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0 2 DA0DADA0.1 DADADADADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0 2 DADA0DADA0.4 DADADADADA DADADADADADADADADADADADADA DADADADADADADADA DADA0 2 DADA0DADA0.4 DADADADADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0 2 DA0DADA0.2 DADADADADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0 2 DA0DADA0.6 DADADADADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0 2 DA0DADA0.3 DADADADADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0 2 DA0DADA0.5 DADADADADADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.1 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.2 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADADADADA DA0DADA0 2 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADADADADA DA0DADA0 4 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADADADADA DA0DADA0 3 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADADADADA DA0DADA0 5 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADA 1 DADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADA 2 DADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.1 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.2 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADA DADADA DADADADADA DADA0DADA0.1 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADA DADADA DADADADADA DADA0DADA0.2 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;6 DADA 8DDHA DA0DADA0.1 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;6 DADA 8DDHA DA0DADA0.4 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;6 DADA 8DDHA DA0DADA0.2 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;6 DADA 8DDHA DA0DADA0.3 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.1 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.2 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DA0DADA0 1 DADADADADADA DADADADA DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.1 DADADADADADA DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.2 DADADADADADA DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.3 DADADADADADA DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADA DADA0DADA0.2 DADADADADADA DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADA DADA0DADA0.1 DADADADADADA DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DADADADA DA0 1 DADADADADADADADADADA DADADADA DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DADADADA DA0 2 DADADADADADADADADADA DADADADA DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.1 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.3 DADADADADA DADADADADADA DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.2 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADA DADADADADADADA DADADADADADA DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;6 DADA 8DDHA DADA0DADA0.1 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;6 DADA 8DDHA DADA0DADA0.2 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DADADADA DADADADADA.1 DADADADA DADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DADADADA DADADADADA.2 DADADADA DADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DADADADA DADADADADA.3 DADADADA DADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DADADADA DADADADADA.4 DADADADA DADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DA0DADA0.1 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DA0DADA0.2 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DA0DADA0.3 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DA0DADA0.4 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DA0DADA0.5 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DA0DADA0.6 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DA0DADA0.7 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0.3 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0.4 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0.5 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0.6 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0.7 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;6 DADA 8DDHA DA0DADA01 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;6 DADA 8DDHA DA0DADA0 2 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0 1 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0 2 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0 3 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0 4 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0 5 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0 6 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0 7 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0.1 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0.2 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0.3 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0.4 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0.2 DADADADADADA DA0DADA0.4</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADADA DADADADA DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADA DA0 1 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.2 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADA DA0DA0 1 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADA DA0DA0 2 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADA DA0DA0 3 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADA DA0DA0 4 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADA DA0DA0 5 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADA DA0DA0 6 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADA DA0DA0 7 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0 2 DADA0DADA0.1 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0 2 DADA0DADA0.2 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0 1 DADA0DADA0.1 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0 1 DADA0DADA0.3 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0 1 DADA0DADA0.2 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0 1 DADA0DADA0.4 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DADADADADADA DADADADA DADA0.1</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DADADADADADA DADADADA DADA0.2</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DADADADADADA DADADADA DADA0.3</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DADADADADADA DADADADA DADA0.4</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DADADADADADA DADADADA DADA0.5</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0 1 DADA0DADA0.DA DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0 1 DADADADADADADADA DADADADA DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADADA DADA DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADA DADA DADADA DADADADA DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 6 DADA 8 DA0DADA0.1 DADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 6 DADA 8 DA0DADA0.2 DADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 6 DADA 8 DA0DADA0.3 DADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 6 DADA 8 DA0DADA0.4 DADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADA DADADA DA0DADA0.1 DADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADA DADADA DA0DADA0.3 DADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADA DADADA DA0DADA0.2 DADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADA DADADA DA0DADA0.4 DADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADA DADADADADADADA DADADADADA DADADADADA DA0DADA0 1 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADA DADADADADADADA DADADADADA DADADADADA DA0DADA0 2 DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0 1 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0 2 DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DADADADADADADA DA0DADA0.1</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DADADADADADADA DA0DADA0.2</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DADADADADADADA DA0DADA0.3</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DADADADADADADA DA0DADA0.4</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0.2 DADADADADADADA DA0DADA0.2</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.1 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.2 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.3 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DADADADADADADA DADADADA DA0DADA0 1</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DADADADADADADA DADADADA DA0DADA0 2</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DADADADADADADA DADADADA DA0DADA0 3</t>
+  </si>
+  <si>
+    <t>PAMCHAYATA GHARA KAMARA NAM0-1 KAILAPURA JASAMAURA</t>
+  </si>
+  <si>
+    <t>PAMCHAYATA GHARA KAMARA NAM0-2 KAILAPURA JASAMAURA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.1 DADADADADADADADADA ;DADADADADDHA DADADADA DADADADADADADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.2 DADADADADADADADADA ;DADADADADDHA DADADADA DADADADADADADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.1 DADADADADADADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;6 DADA 8DDHA DA0DADA0.1 DADADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;6 DADA 8DDHA DA0DADA0.2 DADADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;6 DADA 8DDHA DA0DADA0.3 DADADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;6 DADA 8DDHA DA0DADA0.4 DADADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.2 DADADADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.3 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.4 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADADADA DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADA DADADADADADADADA DADADADADA 3 DADADADADADADA DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADA DADADADADADADADA DADADADADA 1 DADADADADADADA DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADA DADADADADADADADA DADADADADA 2 DADADADADADADA DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.1 DADADADADADADA DADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.3 DADADADADADADA DADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.2 DADADADADADADA DADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADA1 DADADADA DADA0.1 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADA1 DADADADADADADADA DADADADA DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADA1 DADADADA DADA0 2 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADA1 DADADADA DADA0 3 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADA1 DADADADA DADA0 4 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADA DADADA DA0DADA0 1 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADA DADADA DA0DADA0 4 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADA DADADA DA0DADA0 2 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADA DADADA DA0DADA0 6 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADA DADADA DA0DADA0 3 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADA DADADA DA0DADA0 5 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0.3 DADADADA DADA0.DA DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0.3 DA0DADA0.2 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0.3 DA0DADA0.3 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADADA DADADADADA DADADADADA DADA0 DADA0 DA0DADA0 1 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADADA DADADADADA DADADADADA DADA0 DADA0 DA0DADA0 2 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADADA DADADADADA DADADADADA DADA0 DADA0 DA0DADA0 4 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADADA DADADADADA DADADADADA DADA0 DADA0 DA0DADA0 3 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADADADADA DA0DADA0 1 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADADADADA DA0DADA0 4 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADADADADA DA0DADA0 2 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADADADADA DA0DADA0 3 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADADA DADADADADADADA DA0DADA0 3 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADA DADADADADADA DADA DADADA DADADADA DADA0 1 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADA DADADADADADA DADA DADADADA DADA0 3 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADA DADADADADADA DADA DADADA DADADADA DADA0 2 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.3 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.4 DADADADADADA</t>
+  </si>
+  <si>
+    <t>PHAIEJAAMA UCHCHA PRATHAMIKA VIDYALAYA KA0NAM0-3 KITHAUDA</t>
+  </si>
+  <si>
+    <t>PHAIEJAAMA UCHCHA PRATHAMIKA VIDYALAYA KA0NAM0-5 KITHAUDA</t>
+  </si>
+  <si>
+    <t>PHAIEJAAMA UCHCHA PRATHAMIKA VIDYALAYA KA0NAM0-4 KITHAUDA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.1 DADADADADADADADADADADA DADADADA DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADADADA DADADADA DADADADADADADADADADADA DADADADA DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.2 DADADADADADADADADADADA DADADADA DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.1 DADADADADA DADADADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.2 DADADADADA DADADADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.3 DADADADADA DADADADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.4 DADADADADA DADADADADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DA0DADA0 1 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.1 DADADADADADADADA DADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADADDHA DADA0DADA0.2 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADA DADA DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>JU0HA0SKULA JIVANAPURI URPHA UJIYALI KALA</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 ALLUVALA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DA0DADA0.1 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DA0DADA0.2 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.1 DADADADADADADA DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.2 DADADA DADADADA DADADADA DADADADADADADA DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADA1 DADADADADA DADADADA DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADA2 DADADADADA DADADADA DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0 4 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0 5 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0 6 DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.1 DADADADA DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADA DADADADA DADADADA DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.2 DADADADA DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.3 DADADADA DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0 1 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0 2 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0 3 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0 4 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0 5 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0.1 DADADA DADADADA DADADADA DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0 1 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0 3 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0 2 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0 4 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.1 DADADADADADADADADA DADADADA DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.5 DADADADADADADADADA DADADADA DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0DADA0.2 DADADADADADADADADA DADADADA DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADA DADADA DADADADADADA DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADADA DADADA DADADADADADA DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADADADA DADADADADADADADA DADADADADADA DADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DA0DADA0 3 DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADA DADADADADADA DADADADA DADADADADA DA0DADA0 1 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADA DADADADADADA DADADADA DADADADADA DA0DADA0 2 DADADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DADADADADADADA DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DA0DADA0.1 DADADADA DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DA0DADA0.2 DADADADA DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DA0DADA0.1 DADADADADADADADADA DADADADA DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DA0DADA0.2 DADADADADADADADADA DADADADA DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1 DADA 8 DADADADADADADADA DDHA DA0DADA0.3 DADADADADADADADADA DADADADA DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0.1 DADADADADADADADADA DADADADA DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA 1 DADA 8 DADADADADADADADA DA0DADA0.2 DADADADADADADADADA DADADADA DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0 1 DA0DADA0 3 DADADADADA DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0 2 DADADADADA DADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0.3 DA0DADA0.1 DADADADADA DADADADADADADA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0.3 DA0DADA0.2 DADADADADA DADADADADADADA</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -1121,8 +1190,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1138,7 +1215,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1146,12 +1223,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1450,82 +1545,151 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:24">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="D2" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="E2" t="s">
-        <v>347</v>
+        <v>370</v>
       </c>
       <c r="F2" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="G2" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="H2" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="I2" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="J2" t="s">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="K2" t="s">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="L2" t="s">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="M2" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="N2" t="s">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="O2" t="s">
-        <v>357</v>
+        <v>380</v>
       </c>
       <c r="P2" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="Q2" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="R2" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="S2" t="s">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="T2" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="U2" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="V2" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="W2" t="s">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="X2" t="s">
-        <v>366</v>
+        <v>389</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -1533,7 +1697,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>1074</v>
@@ -1607,7 +1771,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>718</v>
@@ -1681,7 +1845,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C5">
         <v>531</v>
@@ -1755,7 +1919,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C6">
         <v>1132</v>
@@ -1829,7 +1993,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>682</v>
@@ -1903,7 +2067,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C8">
         <v>765</v>
@@ -1977,7 +2141,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>726</v>
@@ -2051,7 +2215,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C10">
         <v>758</v>
@@ -2125,7 +2289,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C11">
         <v>678</v>
@@ -2199,7 +2363,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C12">
         <v>672</v>
@@ -2273,7 +2437,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C13">
         <v>819</v>
@@ -2347,7 +2511,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <v>745</v>
@@ -2421,7 +2585,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C15">
         <v>838</v>
@@ -2495,7 +2659,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C16">
         <v>800</v>
@@ -2569,7 +2733,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C17">
         <v>926</v>
@@ -2643,7 +2807,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C18">
         <v>766</v>
@@ -2717,7 +2881,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C19">
         <v>743</v>
@@ -2791,7 +2955,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="C20">
         <v>764</v>
@@ -2865,7 +3029,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="C21">
         <v>861</v>
@@ -2939,7 +3103,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C22">
         <v>808</v>
@@ -3013,7 +3177,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C23">
         <v>743</v>
@@ -3087,7 +3251,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C24">
         <v>663</v>
@@ -3161,7 +3325,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C25">
         <v>625</v>
@@ -3235,7 +3399,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C26">
         <v>619</v>
@@ -3309,7 +3473,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="C27">
         <v>643</v>
@@ -3383,7 +3547,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C28">
         <v>1135</v>
@@ -3457,7 +3621,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C29">
         <v>699</v>
@@ -3531,7 +3695,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C30">
         <v>1097</v>
@@ -3605,7 +3769,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C31">
         <v>772</v>
@@ -3679,7 +3843,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C32">
         <v>789</v>
@@ -3753,7 +3917,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="C33">
         <v>765</v>
@@ -3827,7 +3991,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C34">
         <v>779</v>
@@ -3901,7 +4065,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C35">
         <v>560</v>
@@ -3975,7 +4139,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C36">
         <v>905</v>
@@ -4049,7 +4213,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C37">
         <v>895</v>
@@ -4123,7 +4287,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="C38">
         <v>1106</v>
@@ -4197,7 +4361,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C39">
         <v>1087</v>
@@ -4271,7 +4435,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="C40">
         <v>1004</v>
@@ -4345,7 +4509,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C41">
         <v>1182</v>
@@ -4419,7 +4583,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C42">
         <v>931</v>
@@ -4493,7 +4657,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="C43">
         <v>981</v>
@@ -4567,7 +4731,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="C44">
         <v>853</v>
@@ -4641,7 +4805,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="C45">
         <v>585</v>
@@ -4715,7 +4879,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C46">
         <v>872</v>
@@ -4789,7 +4953,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C47">
         <v>833</v>
@@ -4863,7 +5027,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="C48">
         <v>742</v>
@@ -4937,7 +5101,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C49">
         <v>637</v>
@@ -5011,7 +5175,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C50">
         <v>766</v>
@@ -5085,7 +5249,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="C51">
         <v>842</v>
@@ -5159,7 +5323,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="C52">
         <v>912</v>
@@ -5233,7 +5397,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="C53">
         <v>852</v>
@@ -5307,7 +5471,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="C54">
         <v>907</v>
@@ -5381,7 +5545,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C55">
         <v>742</v>
@@ -5455,7 +5619,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="C56">
         <v>812</v>
@@ -5529,7 +5693,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="C57">
         <v>739</v>
@@ -5603,7 +5767,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="C58">
         <v>660</v>
@@ -5677,7 +5841,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C59">
         <v>647</v>
@@ -5751,7 +5915,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C60">
         <v>746</v>
@@ -5825,7 +5989,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="C61">
         <v>708</v>
@@ -5899,7 +6063,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="C62">
         <v>887</v>
@@ -5973,7 +6137,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="C63">
         <v>680</v>
@@ -6047,7 +6211,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="C64">
         <v>1214</v>
@@ -6121,7 +6285,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="C65">
         <v>1166</v>
@@ -6195,7 +6359,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="C66">
         <v>743</v>
@@ -6269,7 +6433,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="C67">
         <v>960</v>
@@ -6343,7 +6507,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="C68">
         <v>739</v>
@@ -6417,7 +6581,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="C69">
         <v>1202</v>
@@ -6491,7 +6655,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="C70">
         <v>664</v>
@@ -6565,7 +6729,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="C71">
         <v>1225</v>
@@ -6639,7 +6803,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C72">
         <v>638</v>
@@ -6713,7 +6877,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="C73">
         <v>643</v>
@@ -6787,7 +6951,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C74">
         <v>882</v>
@@ -6861,7 +7025,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="C75">
         <v>1079</v>
@@ -6935,7 +7099,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="C76">
         <v>673</v>
@@ -7009,7 +7173,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="C77">
         <v>834</v>
@@ -7083,7 +7247,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="C78">
         <v>682</v>
@@ -7157,7 +7321,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C79">
         <v>975</v>
@@ -7231,7 +7395,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C80">
         <v>947</v>
@@ -7305,7 +7469,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="C81">
         <v>807</v>
@@ -7379,7 +7543,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="C82">
         <v>1167</v>
@@ -7453,7 +7617,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="C83">
         <v>753</v>
@@ -7527,7 +7691,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="C84">
         <v>1209</v>
@@ -7601,7 +7765,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C85">
         <v>1245</v>
@@ -7675,7 +7839,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="C86">
         <v>1068</v>
@@ -7749,7 +7913,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="C87">
         <v>835</v>
@@ -7823,7 +7987,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="C88">
         <v>1006</v>
@@ -7897,7 +8061,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="C89">
         <v>1128</v>
@@ -7971,7 +8135,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="C90">
         <v>1136</v>
@@ -8045,7 +8209,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="C91">
         <v>636</v>
@@ -8119,7 +8283,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="C92">
         <v>677</v>
@@ -8193,7 +8357,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="C93">
         <v>824</v>
@@ -8267,7 +8431,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="C94">
         <v>922</v>
@@ -8341,7 +8505,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="C95">
         <v>809</v>
@@ -8415,7 +8579,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="C96">
         <v>741</v>
@@ -8489,7 +8653,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="C97">
         <v>750</v>
@@ -8563,7 +8727,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="C98">
         <v>623</v>
@@ -8637,7 +8801,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="C99">
         <v>853</v>
@@ -8711,7 +8875,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="C100">
         <v>785</v>
@@ -8785,7 +8949,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="C101">
         <v>841</v>
@@ -8859,7 +9023,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C102">
         <v>710</v>
@@ -8933,7 +9097,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="C103">
         <v>990</v>
@@ -9007,7 +9171,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="C104">
         <v>901</v>
@@ -9081,7 +9245,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="C105">
         <v>924</v>
@@ -9155,7 +9319,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="C106">
         <v>989</v>
@@ -9229,7 +9393,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="C107">
         <v>795</v>
@@ -9303,7 +9467,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="C108">
         <v>572</v>
@@ -9377,7 +9541,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="C109">
         <v>833</v>
@@ -9451,7 +9615,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="C110">
         <v>1223</v>
@@ -9525,7 +9689,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="C111">
         <v>1188</v>
@@ -9599,7 +9763,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="C112">
         <v>1179</v>
@@ -9673,7 +9837,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C113">
         <v>901</v>
@@ -9747,7 +9911,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="C114">
         <v>692</v>
@@ -9821,7 +9985,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="C115">
         <v>919</v>
@@ -9895,7 +10059,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="C116">
         <v>829</v>
@@ -9969,7 +10133,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="C117">
         <v>1196</v>
@@ -10043,7 +10207,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="C118">
         <v>702</v>
@@ -10117,7 +10281,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="C119">
         <v>727</v>
@@ -10191,7 +10355,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="C120">
         <v>818</v>
@@ -10265,7 +10429,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="C121">
         <v>725</v>
@@ -10339,7 +10503,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="C122">
         <v>680</v>
@@ -10413,7 +10577,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="C123">
         <v>713</v>
@@ -10487,7 +10651,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="C124">
         <v>1205</v>
@@ -10561,7 +10725,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="C125">
         <v>540</v>
@@ -10635,7 +10799,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="C126">
         <v>713</v>
@@ -10709,7 +10873,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="C127">
         <v>745</v>
@@ -10783,7 +10947,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="C128">
         <v>658</v>
@@ -10857,7 +11021,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="C129">
         <v>720</v>
@@ -10931,7 +11095,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="C130">
         <v>1106</v>
@@ -11005,7 +11169,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="C131">
         <v>1015</v>
@@ -11079,7 +11243,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="C132">
         <v>734</v>
@@ -11153,7 +11317,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="C133">
         <v>764</v>
@@ -11227,7 +11391,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="C134">
         <v>926</v>
@@ -11301,7 +11465,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="C135">
         <v>987</v>
@@ -11375,7 +11539,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C136">
         <v>1183</v>
@@ -11449,7 +11613,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="C137">
         <v>628</v>
@@ -11523,7 +11687,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="C138">
         <v>630</v>
@@ -11597,7 +11761,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="C139">
         <v>1177</v>
@@ -11671,7 +11835,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="C140">
         <v>1125</v>
@@ -11745,7 +11909,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="C141">
         <v>981</v>
@@ -11819,7 +11983,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="C142">
         <v>923</v>
@@ -11893,7 +12057,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="C143">
         <v>914</v>
@@ -11967,7 +12131,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="C144">
         <v>640</v>
@@ -12041,7 +12205,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="C145">
         <v>1059</v>
@@ -12115,7 +12279,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="C146">
         <v>936</v>
@@ -12189,7 +12353,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="C147">
         <v>660</v>
@@ -12263,7 +12427,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="C148">
         <v>602</v>
@@ -12337,7 +12501,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="C149">
         <v>924</v>
@@ -12411,7 +12575,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="C150">
         <v>1069</v>
@@ -12485,7 +12649,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C151">
         <v>1021</v>
@@ -12559,7 +12723,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="C152">
         <v>906</v>
@@ -12633,7 +12797,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="C153">
         <v>814</v>
@@ -12707,7 +12871,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="C154">
         <v>682</v>
@@ -12781,7 +12945,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C155">
         <v>906</v>
@@ -12855,7 +13019,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="C156">
         <v>741</v>
@@ -12929,7 +13093,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="C157">
         <v>1185</v>
@@ -13003,7 +13167,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="C158">
         <v>701</v>
@@ -13077,7 +13241,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="C159">
         <v>642</v>
@@ -13151,7 +13315,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="C160">
         <v>705</v>
@@ -13225,7 +13389,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="C161">
         <v>687</v>
@@ -13299,7 +13463,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="C162">
         <v>972</v>
@@ -13373,7 +13537,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="C163">
         <v>1162</v>
@@ -13447,7 +13611,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="C164">
         <v>1198</v>
@@ -13521,7 +13685,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="C165">
         <v>1157</v>
@@ -13595,7 +13759,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="C166">
         <v>834</v>
@@ -13669,7 +13833,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="C167">
         <v>730</v>
@@ -13743,7 +13907,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="C168">
         <v>664</v>
@@ -13817,7 +13981,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="C169">
         <v>606</v>
@@ -13891,7 +14055,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="C170">
         <v>1123</v>
@@ -13965,7 +14129,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="C171">
         <v>1022</v>
@@ -14039,7 +14203,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="C172">
         <v>1101</v>
@@ -14113,7 +14277,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="C173">
         <v>1064</v>
@@ -14187,7 +14351,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="C174">
         <v>1141</v>
@@ -14261,7 +14425,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="C175">
         <v>1113</v>
@@ -14335,7 +14499,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="C176">
         <v>1169</v>
@@ -14409,7 +14573,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="C177">
         <v>891</v>
@@ -14483,7 +14647,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="C178">
         <v>577</v>
@@ -14557,7 +14721,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="C179">
         <v>1151</v>
@@ -14631,7 +14795,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="C180">
         <v>862</v>
@@ -14705,7 +14869,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="C181">
         <v>700</v>
@@ -14779,7 +14943,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="C182">
         <v>758</v>
@@ -14853,7 +15017,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="C183">
         <v>687</v>
@@ -14927,7 +15091,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="C184">
         <v>642</v>
@@ -15001,7 +15165,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="C185">
         <v>727</v>
@@ -15075,7 +15239,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="C186">
         <v>739</v>
@@ -15149,7 +15313,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="C187">
         <v>1111</v>
@@ -15223,7 +15387,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="C188">
         <v>1160</v>
@@ -15297,7 +15461,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="C189">
         <v>733</v>
@@ -15371,7 +15535,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="C190">
         <v>719</v>
@@ -15445,7 +15609,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="C191">
         <v>691</v>
@@ -15519,7 +15683,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="C192">
         <v>713</v>
@@ -15593,7 +15757,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="C193">
         <v>1025</v>
@@ -15667,7 +15831,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="C194">
         <v>824</v>
@@ -15741,7 +15905,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="C195">
         <v>786</v>
@@ -15815,7 +15979,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="C196">
         <v>738</v>
@@ -15889,7 +16053,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="C197">
         <v>1100</v>
@@ -15963,7 +16127,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="C198">
         <v>866</v>
@@ -16037,7 +16201,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="C199">
         <v>902</v>
@@ -16111,7 +16275,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="C200">
         <v>892</v>
@@ -16185,7 +16349,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="C201">
         <v>646</v>
@@ -16259,7 +16423,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="C202">
         <v>596</v>
@@ -16333,7 +16497,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="C203">
         <v>1128</v>
@@ -16407,7 +16571,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="C204">
         <v>1126</v>
@@ -16481,7 +16645,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="C205">
         <v>1126</v>
@@ -16555,7 +16719,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="C206">
         <v>815</v>
@@ -16629,7 +16793,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="C207">
         <v>683</v>
@@ -16703,7 +16867,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C208">
         <v>730</v>
@@ -16777,7 +16941,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="C209">
         <v>737</v>
@@ -16851,7 +17015,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="C210">
         <v>679</v>
@@ -16925,7 +17089,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="C211">
         <v>680</v>
@@ -16999,7 +17163,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="C212">
         <v>618</v>
@@ -17073,7 +17237,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="C213">
         <v>610</v>
@@ -17147,7 +17311,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="C214">
         <v>784</v>
@@ -17221,7 +17385,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="C215">
         <v>716</v>
@@ -17295,7 +17459,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="C216">
         <v>707</v>
@@ -17369,7 +17533,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="C217">
         <v>698</v>
@@ -17443,7 +17607,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="C218">
         <v>540</v>
@@ -17517,7 +17681,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="C219">
         <v>1122</v>
@@ -17591,7 +17755,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="C220">
         <v>1033</v>
@@ -17665,7 +17829,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="C221">
         <v>682</v>
@@ -17739,7 +17903,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="C222">
         <v>676</v>
@@ -17813,7 +17977,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="C223">
         <v>1146</v>
@@ -17887,7 +18051,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="C224">
         <v>1013</v>
@@ -17961,7 +18125,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="C225">
         <v>714</v>
@@ -18035,7 +18199,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="C226">
         <v>1064</v>
@@ -18109,7 +18273,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="C227">
         <v>953</v>
@@ -18183,7 +18347,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="C228">
         <v>675</v>
@@ -18257,7 +18421,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="C229">
         <v>698</v>
@@ -18331,7 +18495,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="C230">
         <v>1023</v>
@@ -18405,7 +18569,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="C231">
         <v>1069</v>
@@ -18479,7 +18643,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="C232">
         <v>1132</v>
@@ -18553,7 +18717,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="C233">
         <v>1056</v>
@@ -18627,7 +18791,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="C234">
         <v>1052</v>
@@ -18701,7 +18865,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="C235">
         <v>964</v>
@@ -18775,7 +18939,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="C236">
         <v>775</v>
@@ -18849,7 +19013,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="C237">
         <v>668</v>
@@ -18923,7 +19087,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="C238">
         <v>1198</v>
@@ -18997,7 +19161,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="C239">
         <v>1106</v>
@@ -19071,7 +19235,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="C240">
         <v>737</v>
@@ -19145,7 +19309,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C241">
         <v>732</v>
@@ -19219,7 +19383,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="C242">
         <v>1075</v>
@@ -19293,7 +19457,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="C243">
         <v>1150</v>
@@ -19367,7 +19531,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="C244">
         <v>1000</v>
@@ -19441,7 +19605,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="C245">
         <v>995</v>
@@ -19515,7 +19679,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="C246">
         <v>1189</v>
@@ -19589,7 +19753,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="C247">
         <v>1212</v>
@@ -19663,7 +19827,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="C248">
         <v>790</v>
@@ -19737,7 +19901,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="C249">
         <v>751</v>
@@ -19811,7 +19975,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="C250">
         <v>923</v>
@@ -19885,7 +20049,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="C251">
         <v>614</v>
@@ -19959,7 +20123,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="C252">
         <v>619</v>
@@ -20033,7 +20197,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="C253">
         <v>667</v>
@@ -20107,7 +20271,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="C254">
         <v>593</v>
@@ -20181,7 +20345,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="C255">
         <v>616</v>
@@ -20255,7 +20419,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="C256">
         <v>628</v>
@@ -20329,7 +20493,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="C257">
         <v>567</v>
@@ -20403,7 +20567,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="C258">
         <v>727</v>
@@ -20477,7 +20641,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C259">
         <v>717</v>
@@ -20551,7 +20715,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="C260">
         <v>494</v>
@@ -20625,7 +20789,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="C261">
         <v>1147</v>
@@ -20699,7 +20863,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="C262">
         <v>1154</v>
@@ -20773,7 +20937,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="C263">
         <v>707</v>
@@ -20847,7 +21011,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="C264">
         <v>635</v>
@@ -20921,7 +21085,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="C265">
         <v>739</v>
@@ -20995,7 +21159,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="C266">
         <v>669</v>
@@ -21069,7 +21233,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="C267">
         <v>930</v>
@@ -21143,7 +21307,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="C268">
         <v>881</v>
@@ -21217,7 +21381,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="C269">
         <v>713</v>
@@ -21291,7 +21455,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="C270">
         <v>757</v>
@@ -21365,7 +21529,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="C271">
         <v>1091</v>
@@ -21439,7 +21603,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="C272">
         <v>789</v>
@@ -21513,7 +21677,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="C273">
         <v>803</v>
@@ -21587,7 +21751,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="C274">
         <v>870</v>
@@ -21661,7 +21825,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="C275">
         <v>681</v>
@@ -21735,7 +21899,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="C276">
         <v>722</v>
@@ -21809,7 +21973,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="C277">
         <v>1212</v>
@@ -21883,7 +22047,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="C278">
         <v>996</v>
@@ -21957,7 +22121,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="C279">
         <v>1162</v>
@@ -22031,7 +22195,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="C280">
         <v>1097</v>
@@ -22105,7 +22269,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="C281">
         <v>852</v>
@@ -22179,7 +22343,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="C282">
         <v>854</v>
@@ -22253,7 +22417,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="C283">
         <v>826</v>
@@ -22327,7 +22491,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="C284">
         <v>975</v>
@@ -22401,7 +22565,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C285">
         <v>799</v>
@@ -22475,7 +22639,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="C286">
         <v>721</v>
@@ -22549,7 +22713,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="C287">
         <v>786</v>
@@ -22623,7 +22787,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="C288">
         <v>775</v>
@@ -22697,7 +22861,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="C289">
         <v>1023</v>
@@ -22771,7 +22935,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="C290">
         <v>617</v>
@@ -22845,7 +23009,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="C291">
         <v>578</v>
@@ -22919,7 +23083,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>271</v>
+        <v>294</v>
       </c>
       <c r="C292">
         <v>932</v>
@@ -22993,7 +23157,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="C293">
         <v>1075</v>
@@ -23067,7 +23231,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="C294">
         <v>647</v>
@@ -23141,7 +23305,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="C295">
         <v>722</v>
@@ -23215,7 +23379,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="C296">
         <v>782</v>
@@ -23289,7 +23453,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="C297">
         <v>748</v>
@@ -23363,7 +23527,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>277</v>
+        <v>300</v>
       </c>
       <c r="C298">
         <v>686</v>
@@ -23437,7 +23601,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>278</v>
+        <v>301</v>
       </c>
       <c r="C299">
         <v>780</v>
@@ -23511,7 +23675,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="C300">
         <v>734</v>
@@ -23585,7 +23749,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="C301">
         <v>683</v>
@@ -23659,7 +23823,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>281</v>
+        <v>304</v>
       </c>
       <c r="C302">
         <v>613</v>
@@ -23733,7 +23897,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="C303">
         <v>860</v>
@@ -23807,7 +23971,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="C304">
         <v>783</v>
@@ -23881,7 +24045,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="C305">
         <v>774</v>
@@ -23955,7 +24119,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="C306">
         <v>662</v>
@@ -24029,7 +24193,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="C307">
         <v>742</v>
@@ -24103,7 +24267,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="C308">
         <v>700</v>
@@ -24177,7 +24341,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="C309">
         <v>1056</v>
@@ -24251,7 +24415,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="C310">
         <v>1020</v>
@@ -24325,7 +24489,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="C311">
         <v>985</v>
@@ -24399,7 +24563,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="C312">
         <v>1102</v>
@@ -24473,7 +24637,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="C313">
         <v>1041</v>
@@ -24547,7 +24711,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="C314">
         <v>765</v>
@@ -24621,7 +24785,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="C315">
         <v>640</v>
@@ -24695,7 +24859,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="C316">
         <v>803</v>
@@ -24769,7 +24933,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="C317">
         <v>841</v>
@@ -24843,7 +25007,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="C318">
         <v>645</v>
@@ -24917,7 +25081,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="C319">
         <v>496</v>
@@ -24991,7 +25155,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="C320">
         <v>698</v>
@@ -25065,7 +25229,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="C321">
         <v>535</v>
@@ -25139,7 +25303,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="C322">
         <v>630</v>
@@ -25213,7 +25377,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="C323">
         <v>681</v>
@@ -25287,7 +25451,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="C324">
         <v>1143</v>
@@ -25361,7 +25525,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="C325">
         <v>742</v>
@@ -25435,7 +25599,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="C326">
         <v>980</v>
@@ -25509,7 +25673,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="C327">
         <v>826</v>
@@ -25583,7 +25747,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="C328">
         <v>922</v>
@@ -25657,7 +25821,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="C329">
         <v>830</v>
@@ -25731,7 +25895,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="C330">
         <v>765</v>
@@ -25805,7 +25969,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="C331">
         <v>777</v>
@@ -25879,7 +26043,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="C332">
         <v>857</v>
@@ -25953,7 +26117,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="C333">
         <v>825</v>
@@ -26027,7 +26191,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C334">
         <v>683</v>
@@ -26101,7 +26265,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="C335">
         <v>718</v>
@@ -26175,7 +26339,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="C336">
         <v>768</v>
@@ -26249,7 +26413,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="C337">
         <v>1099</v>
@@ -26323,7 +26487,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="C338">
         <v>1027</v>
@@ -26397,7 +26561,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="C339">
         <v>840</v>
@@ -26471,7 +26635,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="C340">
         <v>595</v>
@@ -26545,7 +26709,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="C341">
         <v>598</v>
@@ -26619,7 +26783,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C342">
         <v>589</v>
@@ -26693,7 +26857,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="C343">
         <v>680</v>
@@ -26767,7 +26931,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="C344">
         <v>647</v>
@@ -26841,7 +27005,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="C345">
         <v>1019</v>
@@ -26915,7 +27079,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>319</v>
+        <v>342</v>
       </c>
       <c r="C346">
         <v>605</v>
@@ -26989,7 +27153,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="C347">
         <v>655</v>
@@ -27063,7 +27227,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="C348">
         <v>665</v>
@@ -27137,7 +27301,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="C349">
         <v>636</v>
@@ -27211,7 +27375,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="C350">
         <v>657</v>
@@ -27285,7 +27449,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>324</v>
+        <v>347</v>
       </c>
       <c r="C351">
         <v>752</v>
@@ -27359,7 +27523,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="C352">
         <v>791</v>
@@ -27433,7 +27597,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="C353">
         <v>630</v>
@@ -27507,7 +27671,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
       <c r="C354">
         <v>944</v>
@@ -27581,7 +27745,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="C355">
         <v>731</v>
@@ -27655,7 +27819,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="C356">
         <v>640</v>
@@ -27729,7 +27893,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="C357">
         <v>628</v>
@@ -27803,7 +27967,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="C358">
         <v>570</v>
@@ -27877,7 +28041,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>330</v>
+        <v>353</v>
       </c>
       <c r="C359">
         <v>366</v>
@@ -27951,7 +28115,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>331</v>
+        <v>354</v>
       </c>
       <c r="C360">
         <v>1135</v>
@@ -28025,7 +28189,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="C361">
         <v>1146</v>
@@ -28099,7 +28263,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="C362">
         <v>1012</v>
@@ -28173,7 +28337,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>333</v>
+        <v>356</v>
       </c>
       <c r="C363">
         <v>1006</v>
@@ -28247,7 +28411,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="C364">
         <v>643</v>
@@ -28321,7 +28485,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>335</v>
+        <v>358</v>
       </c>
       <c r="C365">
         <v>627</v>
@@ -28395,7 +28559,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="C366">
         <v>966</v>
@@ -28469,7 +28633,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="C367">
         <v>772</v>
@@ -28543,7 +28707,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="C368">
         <v>703</v>
@@ -28617,7 +28781,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="C369">
         <v>702</v>
@@ -28691,7 +28855,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="C370">
         <v>832</v>
@@ -28765,7 +28929,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="C371">
         <v>731</v>
@@ -28839,7 +29003,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="C372">
         <v>744</v>
@@ -28913,7 +29077,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="C373">
         <v>727</v>
@@ -28987,7 +29151,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>341</v>
+        <v>364</v>
       </c>
       <c r="C374">
         <v>1066</v>
@@ -29061,7 +29225,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="C375">
         <v>993</v>
@@ -29135,7 +29299,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="C376">
         <v>601</v>
@@ -29209,7 +29373,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="C377">
         <v>628</v>
